--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568444429</v>
+        <v>46157.93098046302</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93098046302</v>
+        <v>46157.93173184683</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93173184683</v>
+        <v>46157.93400267253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400267253</v>
+        <v>46157.93718145951</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718145951</v>
+        <v>46158.28216480933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216480933</v>
+        <v>46158.29681731665</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29681731665</v>
+        <v>46158.29814872694</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814872694</v>
+        <v>46158.33387554716</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387554716</v>
+        <v>46158.36857305327</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857305327</v>
+        <v>46158.37287982945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
